--- a/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N24_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T2485_W0065F0001T0006Z000C1N24_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>93.89117289628291</v>
+        <v>15.25731559564597</v>
       </c>
       <c r="D2" t="n">
-        <v>94.76208679835106</v>
+        <v>15.39883910473205</v>
       </c>
       <c r="E2" t="n">
-        <v>19.5324718764718</v>
+        <v>3.174026679926669</v>
       </c>
       <c r="F2" t="n">
-        <v>23.84789672905447</v>
+        <v>3.875283218471351</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.42480260940967</v>
+        <v>6.569030424029072</v>
       </c>
       <c r="D3" t="n">
-        <v>17.26991603917054</v>
+        <v>2.806361356365213</v>
       </c>
       <c r="E3" t="n">
-        <v>19.5324718764718</v>
+        <v>3.174026679926669</v>
       </c>
       <c r="F3" t="n">
-        <v>23.84789672905447</v>
+        <v>3.875283218471351</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>59.55723508560558</v>
+        <v>9.678050701410907</v>
       </c>
       <c r="D4" t="n">
-        <v>60.49654166431663</v>
+        <v>9.830688020451452</v>
       </c>
       <c r="E4" t="n">
-        <v>19.5324718764718</v>
+        <v>3.174026679926669</v>
       </c>
       <c r="F4" t="n">
-        <v>23.84789672905447</v>
+        <v>3.875283218471351</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.25530633678793</v>
+        <v>5.078987279728039</v>
       </c>
       <c r="D5" t="n">
-        <v>30.92448519736784</v>
+        <v>5.025228844572274</v>
       </c>
       <c r="E5" t="n">
-        <v>19.5324718764718</v>
+        <v>3.174026679926669</v>
       </c>
       <c r="F5" t="n">
-        <v>23.84789672905447</v>
+        <v>3.875283218471351</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>43.05979029589756</v>
+        <v>6.997215923083354</v>
       </c>
       <c r="D6" t="n">
-        <v>42.55230645596338</v>
+        <v>6.914749799094048</v>
       </c>
       <c r="E6" t="n">
-        <v>19.5324718764718</v>
+        <v>3.174026679926669</v>
       </c>
       <c r="F6" t="n">
-        <v>23.84789672905447</v>
+        <v>3.875283218471351</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>60.60023439268701</v>
+        <v>9.847538088811641</v>
       </c>
       <c r="D7" t="n">
-        <v>60.73143903675886</v>
+        <v>9.868858843473314</v>
       </c>
       <c r="E7" t="n">
-        <v>19.5324718764718</v>
+        <v>3.174026679926669</v>
       </c>
       <c r="F7" t="n">
-        <v>23.84789672905447</v>
+        <v>3.875283218471351</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>69.5842267325136</v>
+        <v>11.30743684403346</v>
       </c>
       <c r="D8" t="n">
-        <v>68.83918755383891</v>
+        <v>11.18636797749882</v>
       </c>
       <c r="E8" t="n">
-        <v>19.5324718764718</v>
+        <v>3.174026679926669</v>
       </c>
       <c r="F8" t="n">
-        <v>23.84789672905447</v>
+        <v>3.875283218471351</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
